--- a/samples/workday_hcm_validated_sample.xlsx
+++ b/samples/workday_hcm_validated_sample.xlsx
@@ -427,154 +427,154 @@
     <t>Garcia</t>
   </si>
   <si>
-    <t>1978-09-22</t>
-  </si>
-  <si>
-    <t>1981-09-19</t>
-  </si>
-  <si>
-    <t>1973-05-26</t>
-  </si>
-  <si>
-    <t>1993-04-26</t>
-  </si>
-  <si>
-    <t>1984-11-04</t>
-  </si>
-  <si>
-    <t>1993-06-08</t>
-  </si>
-  <si>
-    <t>1990-11-08</t>
-  </si>
-  <si>
-    <t>1990-02-14</t>
-  </si>
-  <si>
-    <t>1972-08-09</t>
-  </si>
-  <si>
-    <t>1978-03-21</t>
-  </si>
-  <si>
-    <t>1990-02-23</t>
-  </si>
-  <si>
-    <t>1978-07-22</t>
-  </si>
-  <si>
-    <t>2016-05-29</t>
-  </si>
-  <si>
-    <t>1977-03-29</t>
-  </si>
-  <si>
-    <t>1992-08-05</t>
-  </si>
-  <si>
-    <t>1974-09-06</t>
-  </si>
-  <si>
-    <t>1988-01-23</t>
-  </si>
-  <si>
-    <t>1977-07-27</t>
-  </si>
-  <si>
-    <t>1971-03-06</t>
-  </si>
-  <si>
-    <t>1997-07-15</t>
-  </si>
-  <si>
-    <t>1973-07-04</t>
-  </si>
-  <si>
-    <t>1991-05-12</t>
-  </si>
-  <si>
-    <t>1994-02-25</t>
-  </si>
-  <si>
-    <t>1998-06-17</t>
-  </si>
-  <si>
-    <t>1983-11-09</t>
-  </si>
-  <si>
-    <t>1983-06-29</t>
-  </si>
-  <si>
-    <t>1983-06-21</t>
-  </si>
-  <si>
-    <t>1985-10-05</t>
+    <t>1978-09-23</t>
+  </si>
+  <si>
+    <t>1981-09-20</t>
+  </si>
+  <si>
+    <t>1973-05-27</t>
+  </si>
+  <si>
+    <t>1993-04-27</t>
+  </si>
+  <si>
+    <t>1984-11-05</t>
+  </si>
+  <si>
+    <t>1993-06-09</t>
+  </si>
+  <si>
+    <t>1990-11-09</t>
+  </si>
+  <si>
+    <t>1990-02-15</t>
+  </si>
+  <si>
+    <t>1972-08-10</t>
   </si>
   <si>
     <t>1978-03-22</t>
   </si>
   <si>
-    <t>1998-03-05</t>
-  </si>
-  <si>
-    <t>1993-02-22</t>
-  </si>
-  <si>
-    <t>1983-02-03</t>
-  </si>
-  <si>
-    <t>1984-01-27</t>
-  </si>
-  <si>
-    <t>1971-11-23</t>
-  </si>
-  <si>
-    <t>1981-07-12</t>
-  </si>
-  <si>
-    <t>1981-05-26</t>
-  </si>
-  <si>
-    <t>1981-03-02</t>
-  </si>
-  <si>
-    <t>1993-05-15</t>
-  </si>
-  <si>
-    <t>1983-07-19</t>
-  </si>
-  <si>
-    <t>1992-11-23</t>
-  </si>
-  <si>
-    <t>1970-04-21</t>
-  </si>
-  <si>
-    <t>1998-09-14</t>
-  </si>
-  <si>
-    <t>1985-05-09</t>
-  </si>
-  <si>
-    <t>1979-08-02</t>
-  </si>
-  <si>
-    <t>1992-07-14</t>
-  </si>
-  <si>
-    <t>1980-04-14</t>
-  </si>
-  <si>
-    <t>1974-11-17</t>
-  </si>
-  <si>
-    <t>1992-06-25</t>
-  </si>
-  <si>
-    <t>1999-03-22</t>
-  </si>
-  <si>
-    <t>1993-11-11</t>
+    <t>1990-02-24</t>
+  </si>
+  <si>
+    <t>1978-07-23</t>
+  </si>
+  <si>
+    <t>2016-05-30</t>
+  </si>
+  <si>
+    <t>1977-03-30</t>
+  </si>
+  <si>
+    <t>1992-08-06</t>
+  </si>
+  <si>
+    <t>1974-09-07</t>
+  </si>
+  <si>
+    <t>1988-01-24</t>
+  </si>
+  <si>
+    <t>1977-07-28</t>
+  </si>
+  <si>
+    <t>1971-03-07</t>
+  </si>
+  <si>
+    <t>1997-07-16</t>
+  </si>
+  <si>
+    <t>1973-07-05</t>
+  </si>
+  <si>
+    <t>1991-05-13</t>
+  </si>
+  <si>
+    <t>1994-02-26</t>
+  </si>
+  <si>
+    <t>1998-06-18</t>
+  </si>
+  <si>
+    <t>1983-11-10</t>
+  </si>
+  <si>
+    <t>1983-06-30</t>
+  </si>
+  <si>
+    <t>1983-06-22</t>
+  </si>
+  <si>
+    <t>1985-10-06</t>
+  </si>
+  <si>
+    <t>1978-03-23</t>
+  </si>
+  <si>
+    <t>1998-03-06</t>
+  </si>
+  <si>
+    <t>1993-02-23</t>
+  </si>
+  <si>
+    <t>1983-02-04</t>
+  </si>
+  <si>
+    <t>1984-01-28</t>
+  </si>
+  <si>
+    <t>1971-11-24</t>
+  </si>
+  <si>
+    <t>1981-07-13</t>
+  </si>
+  <si>
+    <t>1981-05-27</t>
+  </si>
+  <si>
+    <t>1981-03-03</t>
+  </si>
+  <si>
+    <t>1993-05-16</t>
+  </si>
+  <si>
+    <t>1983-07-20</t>
+  </si>
+  <si>
+    <t>1992-11-24</t>
+  </si>
+  <si>
+    <t>1970-04-22</t>
+  </si>
+  <si>
+    <t>1998-09-15</t>
+  </si>
+  <si>
+    <t>1985-05-10</t>
+  </si>
+  <si>
+    <t>1979-08-03</t>
+  </si>
+  <si>
+    <t>1992-07-15</t>
+  </si>
+  <si>
+    <t>1980-04-15</t>
+  </si>
+  <si>
+    <t>1974-11-18</t>
+  </si>
+  <si>
+    <t>1992-06-26</t>
+  </si>
+  <si>
+    <t>1999-03-23</t>
+  </si>
+  <si>
+    <t>1993-11-12</t>
   </si>
   <si>
     <t>sana.davis@company.com</t>
@@ -874,172 +874,172 @@
     <t>17032751878</t>
   </si>
   <si>
-    <t>2025-03-04</t>
-  </si>
-  <si>
-    <t>2023-11-07</t>
-  </si>
-  <si>
-    <t>2022-06-19</t>
-  </si>
-  <si>
-    <t>2026-11-23</t>
-  </si>
-  <si>
-    <t>2018-10-21</t>
-  </si>
-  <si>
-    <t>2025-09-10</t>
-  </si>
-  <si>
-    <t>2024-09-19</t>
-  </si>
-  <si>
-    <t>2019-04-14</t>
-  </si>
-  <si>
-    <t>2018-09-04</t>
-  </si>
-  <si>
-    <t>2022-12-22</t>
-  </si>
-  <si>
-    <t>2022-11-15</t>
-  </si>
-  <si>
-    <t>2019-07-09</t>
-  </si>
-  <si>
-    <t>2023-09-28</t>
-  </si>
-  <si>
-    <t>2024-11-02</t>
-  </si>
-  <si>
-    <t>2018-12-29</t>
-  </si>
-  <si>
-    <t>2021-05-08</t>
-  </si>
-  <si>
-    <t>2021-12-10</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>2019-10-30</t>
-  </si>
-  <si>
-    <t>2022-10-10</t>
-  </si>
-  <si>
-    <t>2022-12-05</t>
-  </si>
-  <si>
-    <t>2022-06-23</t>
-  </si>
-  <si>
-    <t>2023-05-21</t>
-  </si>
-  <si>
-    <t>2022-03-26</t>
-  </si>
-  <si>
-    <t>2024-05-02</t>
-  </si>
-  <si>
-    <t>2021-02-27</t>
-  </si>
-  <si>
-    <t>2020-04-22</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>2022-12-14</t>
-  </si>
-  <si>
-    <t>2020-03-05</t>
-  </si>
-  <si>
-    <t>2018-12-07</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>2023-03-30</t>
-  </si>
-  <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
-    <t>2021-12-12</t>
-  </si>
-  <si>
-    <t>2021-01-29</t>
-  </si>
-  <si>
-    <t>2022-07-15</t>
-  </si>
-  <si>
-    <t>2025-12-21</t>
-  </si>
-  <si>
-    <t>2019-07-12</t>
-  </si>
-  <si>
-    <t>2024-02-05</t>
-  </si>
-  <si>
-    <t>2026-03-07</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>2022-09-04</t>
-  </si>
-  <si>
-    <t>2023-08-17</t>
-  </si>
-  <si>
-    <t>2021-07-20</t>
-  </si>
-  <si>
-    <t>2024-03-04</t>
+    <t>2025-03-05</t>
+  </si>
+  <si>
+    <t>2023-11-08</t>
+  </si>
+  <si>
+    <t>2022-06-20</t>
+  </si>
+  <si>
+    <t>2026-11-24</t>
+  </si>
+  <si>
+    <t>2018-10-22</t>
+  </si>
+  <si>
+    <t>2025-09-11</t>
+  </si>
+  <si>
+    <t>2024-09-20</t>
+  </si>
+  <si>
+    <t>2019-04-15</t>
+  </si>
+  <si>
+    <t>2018-09-05</t>
+  </si>
+  <si>
+    <t>2022-12-23</t>
+  </si>
+  <si>
+    <t>2022-11-16</t>
+  </si>
+  <si>
+    <t>2019-07-10</t>
+  </si>
+  <si>
+    <t>2023-09-29</t>
+  </si>
+  <si>
+    <t>2024-11-03</t>
+  </si>
+  <si>
+    <t>2018-12-30</t>
+  </si>
+  <si>
+    <t>2021-05-09</t>
+  </si>
+  <si>
+    <t>2021-12-11</t>
+  </si>
+  <si>
+    <t>2025-10-05</t>
+  </si>
+  <si>
+    <t>2019-10-31</t>
+  </si>
+  <si>
+    <t>2022-10-11</t>
+  </si>
+  <si>
+    <t>2022-12-06</t>
+  </si>
+  <si>
+    <t>2022-06-24</t>
+  </si>
+  <si>
+    <t>2023-05-22</t>
+  </si>
+  <si>
+    <t>2022-03-27</t>
+  </si>
+  <si>
+    <t>2024-05-03</t>
+  </si>
+  <si>
+    <t>2021-02-28</t>
+  </si>
+  <si>
+    <t>2020-04-23</t>
+  </si>
+  <si>
+    <t>2025-01-10</t>
+  </si>
+  <si>
+    <t>2022-12-15</t>
+  </si>
+  <si>
+    <t>2020-03-06</t>
+  </si>
+  <si>
+    <t>2018-12-08</t>
+  </si>
+  <si>
+    <t>2025-07-04</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>2021-05-12</t>
   </si>
   <si>
     <t>2023-03-31</t>
   </si>
   <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>2018-06-03</t>
-  </si>
-  <si>
-    <t>1996-06-03</t>
-  </si>
-  <si>
-    <t>2022-05-23</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2025-11-19</t>
-  </si>
-  <si>
-    <t>2026-04-01</t>
+    <t>2021-09-02</t>
+  </si>
+  <si>
+    <t>2021-12-13</t>
+  </si>
+  <si>
+    <t>2021-01-30</t>
+  </si>
+  <si>
+    <t>2022-07-16</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>2019-07-13</t>
+  </si>
+  <si>
+    <t>2024-02-06</t>
+  </si>
+  <si>
+    <t>2026-03-08</t>
+  </si>
+  <si>
+    <t>2021-02-09</t>
+  </si>
+  <si>
+    <t>2022-09-05</t>
+  </si>
+  <si>
+    <t>2023-08-18</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>2024-03-05</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>2020-12-19</t>
+  </si>
+  <si>
+    <t>2018-06-04</t>
+  </si>
+  <si>
+    <t>1996-06-04</t>
+  </si>
+  <si>
+    <t>2022-05-24</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2025-11-20</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
   </si>
   <si>
     <t>Employee</t>
